--- a/customer_service_forms/025_marketplace_seller_interaction_inquiry_form--customer_service_forms.xlsx
+++ b/customer_service_forms/025_marketplace_seller_interaction_inquiry_form--customer_service_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -734,8 +734,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -763,12 +763,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_10,_'label':_'phone_call',_'value':_'phone_call'}</t>
+          <t>phone_call</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 10, 'label': 'Phone Call', 'value': 'phone_call'}</t>
+          <t>Phone Call</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_20,_'label':_'email',_'value':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 20, 'label': 'Email', 'value': 'email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -797,12 +797,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_30,_'label':_'live_chat',_'value':_'live_chat'}</t>
+          <t>live_chat</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 30, 'label': 'Live Chat', 'value': 'live_chat'}</t>
+          <t>Live Chat</t>
         </is>
       </c>
     </row>
@@ -814,12 +814,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_11,_'label':_'not_followed_up',_'value':_'not_followed_up'}</t>
+          <t>not_followed_up</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 11, 'label': 'Not Followed Up', 'value': 'not_followed_up'}</t>
+          <t>Not Followed Up</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_21,_'label':_'followed_up',_'value':_'followed_up'}</t>
+          <t>followed_up</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 21, 'label': 'Followed Up', 'value': 'followed_up'}</t>
+          <t>Followed Up</t>
         </is>
       </c>
     </row>
@@ -848,12 +848,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_31,_'label':_'follow_up_scheduled',_'value':_'follow_up_scheduled'}</t>
+          <t>follow_up_scheduled</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 31, 'label': 'Follow Up Scheduled', 'value': 'follow_up_scheduled'}</t>
+          <t>Follow Up Scheduled</t>
         </is>
       </c>
     </row>
